--- a/public/files/report_card_templates/Grade4-6.xlsx
+++ b/public/files/report_card_templates/Grade4-6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\schoolsys\public\files\report_card_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE700C47-FE9C-402C-91AB-692B9E1632B9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1479C531-9AAB-4338-B0E1-30C52E07DC9B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7545" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -319,7 +319,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -353,19 +353,6 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -458,7 +445,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -469,12 +456,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -484,108 +471,117 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -596,9 +592,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -607,7 +600,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -616,19 +609,19 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -646,25 +639,25 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -677,7 +670,18 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1018,277 +1022,277 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O1" s="31" t="s">
+      <c r="O1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="31"/>
-      <c r="T1" s="31"/>
-      <c r="U1" s="31"/>
-      <c r="V1" s="31"/>
-      <c r="W1" s="31"/>
-      <c r="X1" s="31"/>
-      <c r="Y1" s="31"/>
-      <c r="Z1" s="31"/>
-      <c r="AA1" s="31"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="33"/>
+      <c r="R1" s="33"/>
+      <c r="S1" s="33"/>
+      <c r="T1" s="33"/>
+      <c r="U1" s="33"/>
+      <c r="V1" s="33"/>
+      <c r="W1" s="33"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="33"/>
+      <c r="Z1" s="33"/>
+      <c r="AA1" s="33"/>
     </row>
     <row r="2" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="37"/>
-      <c r="M2" s="37"/>
-      <c r="N2" s="37"/>
-      <c r="O2" s="37"/>
-      <c r="Q2" s="32" t="s">
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
+      <c r="M2" s="39"/>
+      <c r="N2" s="39"/>
+      <c r="O2" s="39"/>
+      <c r="Q2" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
-      <c r="T2" s="32"/>
-      <c r="U2" s="32"/>
-      <c r="V2" s="32"/>
-      <c r="W2" s="32"/>
-      <c r="X2" s="32"/>
-      <c r="Y2" s="32"/>
-      <c r="Z2" s="32"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
+      <c r="T2" s="34"/>
+      <c r="U2" s="34"/>
+      <c r="V2" s="34"/>
+      <c r="W2" s="34"/>
+      <c r="X2" s="34"/>
+      <c r="Y2" s="34"/>
+      <c r="Z2" s="34"/>
     </row>
     <row r="3" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="36"/>
-      <c r="K3" s="36"/>
-      <c r="L3" s="36"/>
-      <c r="M3" s="36"/>
-      <c r="N3" s="36"/>
-      <c r="O3" s="36"/>
-      <c r="P3" s="36"/>
-      <c r="Q3" s="36"/>
-      <c r="R3" s="36"/>
-      <c r="S3" s="36"/>
-      <c r="T3" s="36"/>
-      <c r="U3" s="36"/>
-      <c r="V3" s="34" t="s">
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="38"/>
+      <c r="L3" s="38"/>
+      <c r="M3" s="38"/>
+      <c r="N3" s="38"/>
+      <c r="O3" s="38"/>
+      <c r="P3" s="38"/>
+      <c r="Q3" s="38"/>
+      <c r="R3" s="38"/>
+      <c r="S3" s="38"/>
+      <c r="T3" s="38"/>
+      <c r="U3" s="38"/>
+      <c r="V3" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="W3" s="34"/>
-      <c r="X3" s="34"/>
-      <c r="Y3" s="34"/>
-      <c r="Z3" s="36"/>
-      <c r="AA3" s="36"/>
-      <c r="AB3" s="36"/>
-      <c r="AC3" s="36"/>
-      <c r="AD3" s="36"/>
-      <c r="AE3" s="36"/>
-      <c r="AF3" s="36"/>
-      <c r="AG3" s="36"/>
-      <c r="AH3" s="36"/>
-      <c r="AI3" s="36"/>
-      <c r="AJ3" s="36"/>
-      <c r="AK3" s="36"/>
-      <c r="AL3" s="36"/>
-      <c r="AM3" s="36"/>
-      <c r="AN3" s="36"/>
+      <c r="W3" s="36"/>
+      <c r="X3" s="36"/>
+      <c r="Y3" s="36"/>
+      <c r="Z3" s="38"/>
+      <c r="AA3" s="38"/>
+      <c r="AB3" s="38"/>
+      <c r="AC3" s="38"/>
+      <c r="AD3" s="38"/>
+      <c r="AE3" s="38"/>
+      <c r="AF3" s="38"/>
+      <c r="AG3" s="38"/>
+      <c r="AH3" s="38"/>
+      <c r="AI3" s="38"/>
+      <c r="AJ3" s="38"/>
+      <c r="AK3" s="38"/>
+      <c r="AL3" s="38"/>
+      <c r="AM3" s="38"/>
+      <c r="AN3" s="38"/>
     </row>
     <row r="4" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="33" t="s">
+      <c r="A4" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="33"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38"/>
-      <c r="O4" s="38"/>
-      <c r="P4" s="38"/>
-      <c r="Q4" s="33" t="s">
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="40"/>
+      <c r="K4" s="40"/>
+      <c r="L4" s="40"/>
+      <c r="M4" s="40"/>
+      <c r="N4" s="40"/>
+      <c r="O4" s="40"/>
+      <c r="P4" s="40"/>
+      <c r="Q4" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="R4" s="33"/>
-      <c r="S4" s="33"/>
-      <c r="T4" s="33"/>
-      <c r="U4" s="38"/>
-      <c r="V4" s="38"/>
-      <c r="W4" s="38"/>
-      <c r="X4" s="38"/>
-      <c r="Y4" s="38"/>
-      <c r="Z4" s="38"/>
-      <c r="AA4" s="38"/>
-      <c r="AB4" s="38"/>
-      <c r="AC4" s="38"/>
-      <c r="AD4" s="38"/>
-      <c r="AE4" s="38"/>
-      <c r="AF4" s="38"/>
-      <c r="AG4" s="38"/>
-      <c r="AH4" s="33"/>
-      <c r="AI4" s="33"/>
-      <c r="AJ4" s="33"/>
-      <c r="AK4" s="33"/>
-      <c r="AL4" s="33"/>
-      <c r="AM4" s="33"/>
-      <c r="AN4" s="33"/>
+      <c r="R4" s="35"/>
+      <c r="S4" s="35"/>
+      <c r="T4" s="35"/>
+      <c r="U4" s="40"/>
+      <c r="V4" s="40"/>
+      <c r="W4" s="40"/>
+      <c r="X4" s="40"/>
+      <c r="Y4" s="40"/>
+      <c r="Z4" s="40"/>
+      <c r="AA4" s="40"/>
+      <c r="AB4" s="40"/>
+      <c r="AC4" s="40"/>
+      <c r="AD4" s="40"/>
+      <c r="AE4" s="40"/>
+      <c r="AF4" s="40"/>
+      <c r="AG4" s="40"/>
+      <c r="AH4" s="35"/>
+      <c r="AI4" s="35"/>
+      <c r="AJ4" s="35"/>
+      <c r="AK4" s="35"/>
+      <c r="AL4" s="35"/>
+      <c r="AM4" s="35"/>
+      <c r="AN4" s="35"/>
     </row>
     <row r="5" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="45" t="s">
+      <c r="A5" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="46"/>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="46"/>
-      <c r="K5" s="46"/>
-      <c r="L5" s="46"/>
-      <c r="M5" s="47"/>
-      <c r="N5" s="50" t="s">
+      <c r="B5" s="48"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="48"/>
+      <c r="J5" s="48"/>
+      <c r="K5" s="48"/>
+      <c r="L5" s="48"/>
+      <c r="M5" s="49"/>
+      <c r="N5" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="O5" s="50"/>
-      <c r="P5" s="50"/>
-      <c r="Q5" s="50"/>
-      <c r="R5" s="50"/>
-      <c r="S5" s="50"/>
-      <c r="T5" s="50"/>
-      <c r="U5" s="50"/>
-      <c r="V5" s="50"/>
-      <c r="W5" s="50"/>
-      <c r="X5" s="50"/>
-      <c r="Y5" s="50"/>
-      <c r="Z5" s="50"/>
-      <c r="AA5" s="50"/>
-      <c r="AB5" s="50"/>
-      <c r="AC5" s="50"/>
-      <c r="AD5" s="39" t="s">
+      <c r="O5" s="52"/>
+      <c r="P5" s="52"/>
+      <c r="Q5" s="52"/>
+      <c r="R5" s="52"/>
+      <c r="S5" s="52"/>
+      <c r="T5" s="52"/>
+      <c r="U5" s="52"/>
+      <c r="V5" s="52"/>
+      <c r="W5" s="52"/>
+      <c r="X5" s="52"/>
+      <c r="Y5" s="52"/>
+      <c r="Z5" s="52"/>
+      <c r="AA5" s="52"/>
+      <c r="AB5" s="52"/>
+      <c r="AC5" s="52"/>
+      <c r="AD5" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="AE5" s="40"/>
-      <c r="AF5" s="40"/>
-      <c r="AG5" s="40"/>
-      <c r="AH5" s="40"/>
-      <c r="AI5" s="41"/>
-      <c r="AJ5" s="39" t="s">
+      <c r="AE5" s="42"/>
+      <c r="AF5" s="42"/>
+      <c r="AG5" s="42"/>
+      <c r="AH5" s="42"/>
+      <c r="AI5" s="43"/>
+      <c r="AJ5" s="41" t="s">
         <v>64</v>
       </c>
-      <c r="AK5" s="40"/>
-      <c r="AL5" s="40"/>
-      <c r="AM5" s="40"/>
-      <c r="AN5" s="41"/>
+      <c r="AK5" s="42"/>
+      <c r="AL5" s="42"/>
+      <c r="AM5" s="42"/>
+      <c r="AN5" s="43"/>
     </row>
     <row r="6" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="48"/>
-      <c r="B6" s="33"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="33"/>
-      <c r="K6" s="33"/>
-      <c r="L6" s="33"/>
-      <c r="M6" s="49"/>
-      <c r="N6" s="16" t="s">
+      <c r="A6" s="50"/>
+      <c r="B6" s="35"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="35"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="35"/>
+      <c r="L6" s="35"/>
+      <c r="M6" s="51"/>
+      <c r="N6" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="O6" s="16"/>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="16"/>
-      <c r="R6" s="16" t="s">
+      <c r="O6" s="27"/>
+      <c r="P6" s="27"/>
+      <c r="Q6" s="27"/>
+      <c r="R6" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="S6" s="16"/>
-      <c r="T6" s="16"/>
-      <c r="U6" s="16"/>
-      <c r="V6" s="16" t="s">
+      <c r="S6" s="27"/>
+      <c r="T6" s="27"/>
+      <c r="U6" s="27"/>
+      <c r="V6" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="W6" s="16"/>
-      <c r="X6" s="16"/>
-      <c r="Y6" s="16"/>
-      <c r="Z6" s="16" t="s">
+      <c r="W6" s="27"/>
+      <c r="X6" s="27"/>
+      <c r="Y6" s="27"/>
+      <c r="Z6" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="AA6" s="16"/>
-      <c r="AB6" s="16"/>
-      <c r="AC6" s="16"/>
-      <c r="AD6" s="42"/>
-      <c r="AE6" s="43"/>
-      <c r="AF6" s="43"/>
-      <c r="AG6" s="43"/>
-      <c r="AH6" s="43"/>
-      <c r="AI6" s="44"/>
-      <c r="AJ6" s="42"/>
-      <c r="AK6" s="43"/>
-      <c r="AL6" s="43"/>
-      <c r="AM6" s="43"/>
-      <c r="AN6" s="44"/>
+      <c r="AA6" s="27"/>
+      <c r="AB6" s="27"/>
+      <c r="AC6" s="27"/>
+      <c r="AD6" s="44"/>
+      <c r="AE6" s="45"/>
+      <c r="AF6" s="45"/>
+      <c r="AG6" s="45"/>
+      <c r="AH6" s="45"/>
+      <c r="AI6" s="46"/>
+      <c r="AJ6" s="44"/>
+      <c r="AK6" s="45"/>
+      <c r="AL6" s="45"/>
+      <c r="AM6" s="45"/>
+      <c r="AN6" s="46"/>
     </row>
     <row r="7" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="16"/>
-      <c r="O7" s="16"/>
-      <c r="P7" s="16"/>
-      <c r="Q7" s="16"/>
-      <c r="R7" s="16"/>
-      <c r="S7" s="16"/>
-      <c r="T7" s="16"/>
-      <c r="U7" s="16"/>
-      <c r="V7" s="16"/>
-      <c r="W7" s="16"/>
-      <c r="X7" s="16"/>
-      <c r="Y7" s="16"/>
-      <c r="Z7" s="16"/>
-      <c r="AA7" s="16"/>
-      <c r="AB7" s="16"/>
-      <c r="AC7" s="16"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="30"/>
+      <c r="L7" s="30"/>
+      <c r="M7" s="30"/>
+      <c r="N7" s="27"/>
+      <c r="O7" s="27"/>
+      <c r="P7" s="27"/>
+      <c r="Q7" s="27"/>
+      <c r="R7" s="27"/>
+      <c r="S7" s="27"/>
+      <c r="T7" s="27"/>
+      <c r="U7" s="27"/>
+      <c r="V7" s="27"/>
+      <c r="W7" s="27"/>
+      <c r="X7" s="27"/>
+      <c r="Y7" s="27"/>
+      <c r="Z7" s="27"/>
+      <c r="AA7" s="27"/>
+      <c r="AB7" s="27"/>
+      <c r="AC7" s="27"/>
       <c r="AD7" s="24" t="str">
         <f>IF(COUNT(N7:AC7)=4,SUM(N7:AC7)/4,"")</f>
         <v/>
@@ -1298,47 +1302,47 @@
       <c r="AG7" s="25"/>
       <c r="AH7" s="25"/>
       <c r="AI7" s="26"/>
-      <c r="AJ7" s="21" t="str">
+      <c r="AJ7" s="17" t="str">
         <f>IF(AD7&lt;&gt;"",IF(AD7&gt;=75,"Passed","Failed"),"")</f>
         <v/>
       </c>
-      <c r="AK7" s="22"/>
-      <c r="AL7" s="22"/>
-      <c r="AM7" s="22"/>
-      <c r="AN7" s="23"/>
+      <c r="AK7" s="18"/>
+      <c r="AL7" s="18"/>
+      <c r="AM7" s="18"/>
+      <c r="AN7" s="19"/>
     </row>
     <row r="8" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="16"/>
-      <c r="O8" s="16"/>
-      <c r="P8" s="16"/>
-      <c r="Q8" s="16"/>
-      <c r="R8" s="16"/>
-      <c r="S8" s="16"/>
-      <c r="T8" s="16"/>
-      <c r="U8" s="16"/>
-      <c r="V8" s="16"/>
-      <c r="W8" s="16"/>
-      <c r="X8" s="16"/>
-      <c r="Y8" s="16"/>
-      <c r="Z8" s="16"/>
-      <c r="AA8" s="16"/>
-      <c r="AB8" s="16"/>
-      <c r="AC8" s="16"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="30"/>
+      <c r="K8" s="30"/>
+      <c r="L8" s="30"/>
+      <c r="M8" s="30"/>
+      <c r="N8" s="27"/>
+      <c r="O8" s="27"/>
+      <c r="P8" s="27"/>
+      <c r="Q8" s="27"/>
+      <c r="R8" s="27"/>
+      <c r="S8" s="27"/>
+      <c r="T8" s="27"/>
+      <c r="U8" s="27"/>
+      <c r="V8" s="27"/>
+      <c r="W8" s="27"/>
+      <c r="X8" s="27"/>
+      <c r="Y8" s="27"/>
+      <c r="Z8" s="27"/>
+      <c r="AA8" s="27"/>
+      <c r="AB8" s="27"/>
+      <c r="AC8" s="27"/>
       <c r="AD8" s="24" t="str">
         <f t="shared" ref="AD8:AD20" si="0">IF(COUNT(N8:AC8)=4,SUM(N8:AC8)/4,"")</f>
         <v/>
@@ -1348,47 +1352,47 @@
       <c r="AG8" s="25"/>
       <c r="AH8" s="25"/>
       <c r="AI8" s="26"/>
-      <c r="AJ8" s="21" t="str">
+      <c r="AJ8" s="17" t="str">
         <f t="shared" ref="AJ8:AJ20" si="1">IF(AD8&lt;&gt;"",IF(AD8&gt;=75,"Passed","Failed"),"")</f>
         <v/>
       </c>
-      <c r="AK8" s="22"/>
-      <c r="AL8" s="22"/>
-      <c r="AM8" s="22"/>
-      <c r="AN8" s="23"/>
+      <c r="AK8" s="18"/>
+      <c r="AL8" s="18"/>
+      <c r="AM8" s="18"/>
+      <c r="AN8" s="19"/>
     </row>
     <row r="9" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="16"/>
-      <c r="O9" s="16"/>
-      <c r="P9" s="16"/>
-      <c r="Q9" s="16"/>
-      <c r="R9" s="16"/>
-      <c r="S9" s="16"/>
-      <c r="T9" s="16"/>
-      <c r="U9" s="16"/>
-      <c r="V9" s="16"/>
-      <c r="W9" s="16"/>
-      <c r="X9" s="16"/>
-      <c r="Y9" s="16"/>
-      <c r="Z9" s="16"/>
-      <c r="AA9" s="16"/>
-      <c r="AB9" s="16"/>
-      <c r="AC9" s="16"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="30"/>
+      <c r="L9" s="30"/>
+      <c r="M9" s="30"/>
+      <c r="N9" s="27"/>
+      <c r="O9" s="27"/>
+      <c r="P9" s="27"/>
+      <c r="Q9" s="27"/>
+      <c r="R9" s="27"/>
+      <c r="S9" s="27"/>
+      <c r="T9" s="27"/>
+      <c r="U9" s="27"/>
+      <c r="V9" s="27"/>
+      <c r="W9" s="27"/>
+      <c r="X9" s="27"/>
+      <c r="Y9" s="27"/>
+      <c r="Z9" s="27"/>
+      <c r="AA9" s="27"/>
+      <c r="AB9" s="27"/>
+      <c r="AC9" s="27"/>
       <c r="AD9" s="24" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1398,47 +1402,47 @@
       <c r="AG9" s="25"/>
       <c r="AH9" s="25"/>
       <c r="AI9" s="26"/>
-      <c r="AJ9" s="21" t="str">
+      <c r="AJ9" s="17" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AK9" s="22"/>
-      <c r="AL9" s="22"/>
-      <c r="AM9" s="22"/>
-      <c r="AN9" s="23"/>
+      <c r="AK9" s="18"/>
+      <c r="AL9" s="18"/>
+      <c r="AM9" s="18"/>
+      <c r="AN9" s="19"/>
     </row>
     <row r="10" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="16"/>
-      <c r="O10" s="16"/>
-      <c r="P10" s="16"/>
-      <c r="Q10" s="16"/>
-      <c r="R10" s="16"/>
-      <c r="S10" s="16"/>
-      <c r="T10" s="16"/>
-      <c r="U10" s="16"/>
-      <c r="V10" s="16"/>
-      <c r="W10" s="16"/>
-      <c r="X10" s="16"/>
-      <c r="Y10" s="16"/>
-      <c r="Z10" s="16"/>
-      <c r="AA10" s="16"/>
-      <c r="AB10" s="16"/>
-      <c r="AC10" s="16"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="30"/>
+      <c r="J10" s="30"/>
+      <c r="K10" s="30"/>
+      <c r="L10" s="30"/>
+      <c r="M10" s="30"/>
+      <c r="N10" s="27"/>
+      <c r="O10" s="27"/>
+      <c r="P10" s="27"/>
+      <c r="Q10" s="27"/>
+      <c r="R10" s="27"/>
+      <c r="S10" s="27"/>
+      <c r="T10" s="27"/>
+      <c r="U10" s="27"/>
+      <c r="V10" s="27"/>
+      <c r="W10" s="27"/>
+      <c r="X10" s="27"/>
+      <c r="Y10" s="27"/>
+      <c r="Z10" s="27"/>
+      <c r="AA10" s="27"/>
+      <c r="AB10" s="27"/>
+      <c r="AC10" s="27"/>
       <c r="AD10" s="24" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1448,47 +1452,47 @@
       <c r="AG10" s="25"/>
       <c r="AH10" s="25"/>
       <c r="AI10" s="26"/>
-      <c r="AJ10" s="21" t="str">
+      <c r="AJ10" s="17" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AK10" s="22"/>
-      <c r="AL10" s="22"/>
-      <c r="AM10" s="22"/>
-      <c r="AN10" s="23"/>
+      <c r="AK10" s="18"/>
+      <c r="AL10" s="18"/>
+      <c r="AM10" s="18"/>
+      <c r="AN10" s="19"/>
     </row>
     <row r="11" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="16"/>
-      <c r="O11" s="16"/>
-      <c r="P11" s="16"/>
-      <c r="Q11" s="16"/>
-      <c r="R11" s="16"/>
-      <c r="S11" s="16"/>
-      <c r="T11" s="16"/>
-      <c r="U11" s="16"/>
-      <c r="V11" s="16"/>
-      <c r="W11" s="16"/>
-      <c r="X11" s="16"/>
-      <c r="Y11" s="16"/>
-      <c r="Z11" s="16"/>
-      <c r="AA11" s="16"/>
-      <c r="AB11" s="16"/>
-      <c r="AC11" s="16"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="30"/>
+      <c r="K11" s="30"/>
+      <c r="L11" s="30"/>
+      <c r="M11" s="30"/>
+      <c r="N11" s="27"/>
+      <c r="O11" s="27"/>
+      <c r="P11" s="27"/>
+      <c r="Q11" s="27"/>
+      <c r="R11" s="27"/>
+      <c r="S11" s="27"/>
+      <c r="T11" s="27"/>
+      <c r="U11" s="27"/>
+      <c r="V11" s="27"/>
+      <c r="W11" s="27"/>
+      <c r="X11" s="27"/>
+      <c r="Y11" s="27"/>
+      <c r="Z11" s="27"/>
+      <c r="AA11" s="27"/>
+      <c r="AB11" s="27"/>
+      <c r="AC11" s="27"/>
       <c r="AD11" s="24" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1498,47 +1502,47 @@
       <c r="AG11" s="25"/>
       <c r="AH11" s="25"/>
       <c r="AI11" s="26"/>
-      <c r="AJ11" s="21" t="str">
+      <c r="AJ11" s="17" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AK11" s="22"/>
-      <c r="AL11" s="22"/>
-      <c r="AM11" s="22"/>
-      <c r="AN11" s="23"/>
+      <c r="AK11" s="18"/>
+      <c r="AL11" s="18"/>
+      <c r="AM11" s="18"/>
+      <c r="AN11" s="19"/>
     </row>
     <row r="12" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="30" t="s">
+      <c r="A12" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="30"/>
-      <c r="K12" s="30"/>
-      <c r="L12" s="30"/>
-      <c r="M12" s="30"/>
-      <c r="N12" s="16"/>
-      <c r="O12" s="16"/>
-      <c r="P12" s="16"/>
-      <c r="Q12" s="16"/>
-      <c r="R12" s="16"/>
-      <c r="S12" s="16"/>
-      <c r="T12" s="16"/>
-      <c r="U12" s="16"/>
-      <c r="V12" s="16"/>
-      <c r="W12" s="16"/>
-      <c r="X12" s="16"/>
-      <c r="Y12" s="16"/>
-      <c r="Z12" s="16"/>
-      <c r="AA12" s="16"/>
-      <c r="AB12" s="16"/>
-      <c r="AC12" s="16"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="32"/>
+      <c r="J12" s="32"/>
+      <c r="K12" s="32"/>
+      <c r="L12" s="32"/>
+      <c r="M12" s="32"/>
+      <c r="N12" s="27"/>
+      <c r="O12" s="27"/>
+      <c r="P12" s="27"/>
+      <c r="Q12" s="27"/>
+      <c r="R12" s="27"/>
+      <c r="S12" s="27"/>
+      <c r="T12" s="27"/>
+      <c r="U12" s="27"/>
+      <c r="V12" s="27"/>
+      <c r="W12" s="27"/>
+      <c r="X12" s="27"/>
+      <c r="Y12" s="27"/>
+      <c r="Z12" s="27"/>
+      <c r="AA12" s="27"/>
+      <c r="AB12" s="27"/>
+      <c r="AC12" s="27"/>
       <c r="AD12" s="24" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1548,47 +1552,47 @@
       <c r="AG12" s="25"/>
       <c r="AH12" s="25"/>
       <c r="AI12" s="26"/>
-      <c r="AJ12" s="21" t="str">
+      <c r="AJ12" s="17" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AK12" s="22"/>
-      <c r="AL12" s="22"/>
-      <c r="AM12" s="22"/>
-      <c r="AN12" s="23"/>
+      <c r="AK12" s="18"/>
+      <c r="AL12" s="18"/>
+      <c r="AM12" s="18"/>
+      <c r="AN12" s="19"/>
     </row>
     <row r="13" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="16"/>
-      <c r="P13" s="16"/>
-      <c r="Q13" s="16"/>
-      <c r="R13" s="16"/>
-      <c r="S13" s="16"/>
-      <c r="T13" s="16"/>
-      <c r="U13" s="16"/>
-      <c r="V13" s="16"/>
-      <c r="W13" s="16"/>
-      <c r="X13" s="16"/>
-      <c r="Y13" s="16"/>
-      <c r="Z13" s="16"/>
-      <c r="AA13" s="16"/>
-      <c r="AB13" s="16"/>
-      <c r="AC13" s="16"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="30"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="30"/>
+      <c r="K13" s="30"/>
+      <c r="L13" s="30"/>
+      <c r="M13" s="30"/>
+      <c r="N13" s="27"/>
+      <c r="O13" s="27"/>
+      <c r="P13" s="27"/>
+      <c r="Q13" s="27"/>
+      <c r="R13" s="27"/>
+      <c r="S13" s="27"/>
+      <c r="T13" s="27"/>
+      <c r="U13" s="27"/>
+      <c r="V13" s="27"/>
+      <c r="W13" s="27"/>
+      <c r="X13" s="27"/>
+      <c r="Y13" s="27"/>
+      <c r="Z13" s="27"/>
+      <c r="AA13" s="27"/>
+      <c r="AB13" s="27"/>
+      <c r="AC13" s="27"/>
       <c r="AD13" s="24" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1598,14 +1602,14 @@
       <c r="AG13" s="25"/>
       <c r="AH13" s="25"/>
       <c r="AI13" s="26"/>
-      <c r="AJ13" s="21" t="str">
+      <c r="AJ13" s="17" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AK13" s="22"/>
-      <c r="AL13" s="22"/>
-      <c r="AM13" s="22"/>
-      <c r="AN13" s="23"/>
+      <c r="AK13" s="18"/>
+      <c r="AL13" s="18"/>
+      <c r="AM13" s="18"/>
+      <c r="AN13" s="19"/>
     </row>
     <row r="14" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6"/>
@@ -1623,22 +1627,22 @@
       <c r="K14" s="12"/>
       <c r="L14" s="12"/>
       <c r="M14" s="13"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="16"/>
-      <c r="P14" s="16"/>
-      <c r="Q14" s="16"/>
-      <c r="R14" s="16"/>
-      <c r="S14" s="16"/>
-      <c r="T14" s="16"/>
-      <c r="U14" s="16"/>
-      <c r="V14" s="16"/>
-      <c r="W14" s="16"/>
-      <c r="X14" s="16"/>
-      <c r="Y14" s="16"/>
-      <c r="Z14" s="16"/>
-      <c r="AA14" s="16"/>
-      <c r="AB14" s="16"/>
-      <c r="AC14" s="16"/>
+      <c r="N14" s="27"/>
+      <c r="O14" s="27"/>
+      <c r="P14" s="27"/>
+      <c r="Q14" s="27"/>
+      <c r="R14" s="27"/>
+      <c r="S14" s="27"/>
+      <c r="T14" s="27"/>
+      <c r="U14" s="27"/>
+      <c r="V14" s="27"/>
+      <c r="W14" s="27"/>
+      <c r="X14" s="27"/>
+      <c r="Y14" s="27"/>
+      <c r="Z14" s="27"/>
+      <c r="AA14" s="27"/>
+      <c r="AB14" s="27"/>
+      <c r="AC14" s="27"/>
       <c r="AD14" s="24" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1648,14 +1652,14 @@
       <c r="AG14" s="25"/>
       <c r="AH14" s="25"/>
       <c r="AI14" s="26"/>
-      <c r="AJ14" s="21" t="str">
+      <c r="AJ14" s="17" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AK14" s="22"/>
-      <c r="AL14" s="22"/>
-      <c r="AM14" s="22"/>
-      <c r="AN14" s="23"/>
+      <c r="AK14" s="18"/>
+      <c r="AL14" s="18"/>
+      <c r="AM14" s="18"/>
+      <c r="AN14" s="19"/>
     </row>
     <row r="15" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
@@ -1673,22 +1677,22 @@
       <c r="K15" s="12"/>
       <c r="L15" s="12"/>
       <c r="M15" s="13"/>
-      <c r="N15" s="23"/>
-      <c r="O15" s="16"/>
-      <c r="P15" s="16"/>
-      <c r="Q15" s="16"/>
-      <c r="R15" s="16"/>
-      <c r="S15" s="16"/>
-      <c r="T15" s="16"/>
-      <c r="U15" s="16"/>
-      <c r="V15" s="16"/>
-      <c r="W15" s="16"/>
-      <c r="X15" s="16"/>
-      <c r="Y15" s="16"/>
-      <c r="Z15" s="16"/>
-      <c r="AA15" s="16"/>
-      <c r="AB15" s="16"/>
-      <c r="AC15" s="16"/>
+      <c r="N15" s="27"/>
+      <c r="O15" s="27"/>
+      <c r="P15" s="27"/>
+      <c r="Q15" s="27"/>
+      <c r="R15" s="27"/>
+      <c r="S15" s="27"/>
+      <c r="T15" s="27"/>
+      <c r="U15" s="27"/>
+      <c r="V15" s="27"/>
+      <c r="W15" s="27"/>
+      <c r="X15" s="27"/>
+      <c r="Y15" s="27"/>
+      <c r="Z15" s="27"/>
+      <c r="AA15" s="27"/>
+      <c r="AB15" s="27"/>
+      <c r="AC15" s="27"/>
       <c r="AD15" s="24" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1698,14 +1702,14 @@
       <c r="AG15" s="25"/>
       <c r="AH15" s="25"/>
       <c r="AI15" s="26"/>
-      <c r="AJ15" s="21" t="str">
+      <c r="AJ15" s="17" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AK15" s="22"/>
-      <c r="AL15" s="22"/>
-      <c r="AM15" s="22"/>
-      <c r="AN15" s="23"/>
+      <c r="AK15" s="18"/>
+      <c r="AL15" s="18"/>
+      <c r="AM15" s="18"/>
+      <c r="AN15" s="19"/>
     </row>
     <row r="16" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
@@ -1723,22 +1727,22 @@
       <c r="K16" s="12"/>
       <c r="L16" s="12"/>
       <c r="M16" s="13"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="16"/>
-      <c r="P16" s="16"/>
-      <c r="Q16" s="16"/>
-      <c r="R16" s="16"/>
-      <c r="S16" s="16"/>
-      <c r="T16" s="16"/>
-      <c r="U16" s="16"/>
-      <c r="V16" s="16"/>
-      <c r="W16" s="16"/>
-      <c r="X16" s="16"/>
-      <c r="Y16" s="16"/>
-      <c r="Z16" s="16"/>
-      <c r="AA16" s="16"/>
-      <c r="AB16" s="16"/>
-      <c r="AC16" s="16"/>
+      <c r="N16" s="27"/>
+      <c r="O16" s="27"/>
+      <c r="P16" s="27"/>
+      <c r="Q16" s="27"/>
+      <c r="R16" s="27"/>
+      <c r="S16" s="27"/>
+      <c r="T16" s="27"/>
+      <c r="U16" s="27"/>
+      <c r="V16" s="27"/>
+      <c r="W16" s="27"/>
+      <c r="X16" s="27"/>
+      <c r="Y16" s="27"/>
+      <c r="Z16" s="27"/>
+      <c r="AA16" s="27"/>
+      <c r="AB16" s="27"/>
+      <c r="AC16" s="27"/>
       <c r="AD16" s="24" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1748,14 +1752,14 @@
       <c r="AG16" s="25"/>
       <c r="AH16" s="25"/>
       <c r="AI16" s="26"/>
-      <c r="AJ16" s="21" t="str">
+      <c r="AJ16" s="17" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AK16" s="22"/>
-      <c r="AL16" s="22"/>
-      <c r="AM16" s="22"/>
-      <c r="AN16" s="23"/>
+      <c r="AK16" s="18"/>
+      <c r="AL16" s="18"/>
+      <c r="AM16" s="18"/>
+      <c r="AN16" s="19"/>
     </row>
     <row r="17" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6"/>
@@ -1773,22 +1777,22 @@
       <c r="K17" s="12"/>
       <c r="L17" s="12"/>
       <c r="M17" s="13"/>
-      <c r="N17" s="16"/>
-      <c r="O17" s="16"/>
-      <c r="P17" s="16"/>
-      <c r="Q17" s="16"/>
-      <c r="R17" s="16"/>
-      <c r="S17" s="16"/>
-      <c r="T17" s="16"/>
-      <c r="U17" s="16"/>
-      <c r="V17" s="16"/>
-      <c r="W17" s="16"/>
-      <c r="X17" s="16"/>
-      <c r="Y17" s="16"/>
-      <c r="Z17" s="16"/>
-      <c r="AA17" s="16"/>
-      <c r="AB17" s="16"/>
-      <c r="AC17" s="16"/>
+      <c r="N17" s="27"/>
+      <c r="O17" s="27"/>
+      <c r="P17" s="27"/>
+      <c r="Q17" s="27"/>
+      <c r="R17" s="27"/>
+      <c r="S17" s="27"/>
+      <c r="T17" s="27"/>
+      <c r="U17" s="27"/>
+      <c r="V17" s="27"/>
+      <c r="W17" s="27"/>
+      <c r="X17" s="27"/>
+      <c r="Y17" s="27"/>
+      <c r="Z17" s="27"/>
+      <c r="AA17" s="27"/>
+      <c r="AB17" s="27"/>
+      <c r="AC17" s="27"/>
       <c r="AD17" s="24" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1798,14 +1802,14 @@
       <c r="AG17" s="25"/>
       <c r="AH17" s="25"/>
       <c r="AI17" s="26"/>
-      <c r="AJ17" s="21" t="str">
+      <c r="AJ17" s="17" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AK17" s="22"/>
-      <c r="AL17" s="22"/>
-      <c r="AM17" s="22"/>
-      <c r="AN17" s="23"/>
+      <c r="AK17" s="18"/>
+      <c r="AL17" s="18"/>
+      <c r="AM17" s="18"/>
+      <c r="AN17" s="19"/>
     </row>
     <row r="18" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
@@ -1823,22 +1827,22 @@
       <c r="K18" s="12"/>
       <c r="L18" s="12"/>
       <c r="M18" s="13"/>
-      <c r="N18" s="21"/>
-      <c r="O18" s="22"/>
-      <c r="P18" s="22"/>
-      <c r="Q18" s="23"/>
-      <c r="R18" s="21"/>
-      <c r="S18" s="22"/>
-      <c r="T18" s="22"/>
-      <c r="U18" s="23"/>
-      <c r="V18" s="21"/>
-      <c r="W18" s="22"/>
-      <c r="X18" s="22"/>
-      <c r="Y18" s="23"/>
-      <c r="Z18" s="21"/>
-      <c r="AA18" s="22"/>
-      <c r="AB18" s="22"/>
-      <c r="AC18" s="23"/>
+      <c r="N18" s="27"/>
+      <c r="O18" s="27"/>
+      <c r="P18" s="27"/>
+      <c r="Q18" s="27"/>
+      <c r="R18" s="27"/>
+      <c r="S18" s="27"/>
+      <c r="T18" s="27"/>
+      <c r="U18" s="27"/>
+      <c r="V18" s="27"/>
+      <c r="W18" s="27"/>
+      <c r="X18" s="27"/>
+      <c r="Y18" s="27"/>
+      <c r="Z18" s="27"/>
+      <c r="AA18" s="27"/>
+      <c r="AB18" s="27"/>
+      <c r="AC18" s="27"/>
       <c r="AD18" s="24" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1848,47 +1852,47 @@
       <c r="AG18" s="25"/>
       <c r="AH18" s="25"/>
       <c r="AI18" s="26"/>
-      <c r="AJ18" s="21" t="str">
+      <c r="AJ18" s="17" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AK18" s="22"/>
-      <c r="AL18" s="22"/>
-      <c r="AM18" s="22"/>
-      <c r="AN18" s="23"/>
+      <c r="AK18" s="18"/>
+      <c r="AL18" s="18"/>
+      <c r="AM18" s="18"/>
+      <c r="AN18" s="19"/>
     </row>
     <row r="19" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="15"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="15"/>
-      <c r="N19" s="16"/>
-      <c r="O19" s="16"/>
-      <c r="P19" s="16"/>
-      <c r="Q19" s="16"/>
-      <c r="R19" s="16"/>
-      <c r="S19" s="16"/>
-      <c r="T19" s="16"/>
-      <c r="U19" s="16"/>
-      <c r="V19" s="16"/>
-      <c r="W19" s="16"/>
-      <c r="X19" s="16"/>
-      <c r="Y19" s="16"/>
-      <c r="Z19" s="16"/>
-      <c r="AA19" s="16"/>
-      <c r="AB19" s="16"/>
-      <c r="AC19" s="16"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="30"/>
+      <c r="L19" s="30"/>
+      <c r="M19" s="30"/>
+      <c r="N19" s="27"/>
+      <c r="O19" s="27"/>
+      <c r="P19" s="27"/>
+      <c r="Q19" s="27"/>
+      <c r="R19" s="27"/>
+      <c r="S19" s="27"/>
+      <c r="T19" s="27"/>
+      <c r="U19" s="27"/>
+      <c r="V19" s="27"/>
+      <c r="W19" s="27"/>
+      <c r="X19" s="27"/>
+      <c r="Y19" s="27"/>
+      <c r="Z19" s="27"/>
+      <c r="AA19" s="27"/>
+      <c r="AB19" s="27"/>
+      <c r="AC19" s="27"/>
       <c r="AD19" s="24" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1898,20 +1902,20 @@
       <c r="AG19" s="25"/>
       <c r="AH19" s="25"/>
       <c r="AI19" s="26"/>
-      <c r="AJ19" s="21" t="str">
-        <f t="shared" ref="AJ19" si="2">IF(AD19&lt;&gt;"",IF(AD19&gt;=75,"Passed","Failed"),"")</f>
+      <c r="AJ19" s="17" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AK19" s="22"/>
-      <c r="AL19" s="22"/>
-      <c r="AM19" s="22"/>
-      <c r="AN19" s="23"/>
+      <c r="AK19" s="18"/>
+      <c r="AL19" s="18"/>
+      <c r="AM19" s="18"/>
+      <c r="AN19" s="19"/>
     </row>
     <row r="20" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="B20" s="14"/>
+      <c r="B20" s="15"/>
       <c r="C20" s="15"/>
       <c r="D20" s="15"/>
       <c r="E20" s="15"/>
@@ -1922,23 +1926,23 @@
       <c r="J20" s="15"/>
       <c r="K20" s="15"/>
       <c r="L20" s="15"/>
-      <c r="M20" s="15"/>
-      <c r="N20" s="16"/>
-      <c r="O20" s="16"/>
-      <c r="P20" s="16"/>
-      <c r="Q20" s="16"/>
-      <c r="R20" s="16"/>
-      <c r="S20" s="16"/>
-      <c r="T20" s="16"/>
-      <c r="U20" s="16"/>
-      <c r="V20" s="16"/>
-      <c r="W20" s="16"/>
-      <c r="X20" s="16"/>
-      <c r="Y20" s="16"/>
-      <c r="Z20" s="16"/>
-      <c r="AA20" s="16"/>
-      <c r="AB20" s="16"/>
-      <c r="AC20" s="16"/>
+      <c r="M20" s="16"/>
+      <c r="N20" s="27"/>
+      <c r="O20" s="27"/>
+      <c r="P20" s="27"/>
+      <c r="Q20" s="27"/>
+      <c r="R20" s="27"/>
+      <c r="S20" s="27"/>
+      <c r="T20" s="27"/>
+      <c r="U20" s="27"/>
+      <c r="V20" s="27"/>
+      <c r="W20" s="27"/>
+      <c r="X20" s="27"/>
+      <c r="Y20" s="27"/>
+      <c r="Z20" s="27"/>
+      <c r="AA20" s="27"/>
+      <c r="AB20" s="27"/>
+      <c r="AC20" s="27"/>
       <c r="AD20" s="24" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1948,114 +1952,114 @@
       <c r="AG20" s="25"/>
       <c r="AH20" s="25"/>
       <c r="AI20" s="26"/>
-      <c r="AJ20" s="21" t="str">
+      <c r="AJ20" s="17" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AK20" s="22"/>
-      <c r="AL20" s="22"/>
-      <c r="AM20" s="22"/>
-      <c r="AN20" s="23"/>
+      <c r="AK20" s="18"/>
+      <c r="AL20" s="18"/>
+      <c r="AM20" s="18"/>
+      <c r="AN20" s="19"/>
     </row>
     <row r="21" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6"/>
       <c r="B21" s="7"/>
-      <c r="C21" s="17" t="s">
+      <c r="C21" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="18"/>
-      <c r="I21" s="18"/>
-      <c r="J21" s="18"/>
-      <c r="K21" s="18"/>
-      <c r="L21" s="18"/>
-      <c r="M21" s="18"/>
-      <c r="N21" s="60" t="str">
-        <f>IF($AD22&lt;&gt;"", SUM(N7:Q13,N18)/8,"")</f>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="21"/>
+      <c r="K21" s="21"/>
+      <c r="L21" s="21"/>
+      <c r="M21" s="21"/>
+      <c r="N21" s="62" t="str">
+        <f>IF(SUM(N7:Q13,N18)/8 &gt; 0,SUM(N7:Q13,N18)/8,"")</f>
         <v/>
       </c>
-      <c r="O21" s="60"/>
-      <c r="P21" s="60"/>
-      <c r="Q21" s="60"/>
-      <c r="R21" s="60" t="str">
-        <f t="shared" ref="R21" si="3">IF($AD22&lt;&gt;"", SUM(R7:U13,R18)/8,"")</f>
+      <c r="O21" s="62"/>
+      <c r="P21" s="62"/>
+      <c r="Q21" s="62"/>
+      <c r="R21" s="62" t="str">
+        <f t="shared" ref="R21" si="2">IF(SUM(R7:U13,R18)/8 &gt; 0,SUM(R7:U13,R18)/8,"")</f>
         <v/>
       </c>
-      <c r="S21" s="60"/>
-      <c r="T21" s="60"/>
-      <c r="U21" s="60"/>
-      <c r="V21" s="60" t="str">
-        <f t="shared" ref="V21" si="4">IF($AD22&lt;&gt;"", SUM(V7:Y13,V18)/8,"")</f>
+      <c r="S21" s="62"/>
+      <c r="T21" s="62"/>
+      <c r="U21" s="62"/>
+      <c r="V21" s="62" t="str">
+        <f t="shared" ref="V21" si="3">IF(SUM(V7:Y13,V18)/8 &gt; 0,SUM(V7:Y13,V18)/8,"")</f>
         <v/>
       </c>
-      <c r="W21" s="60"/>
-      <c r="X21" s="60"/>
-      <c r="Y21" s="60"/>
-      <c r="Z21" s="60" t="str">
-        <f t="shared" ref="Z21" si="5">IF($AD22&lt;&gt;"", SUM(Z7:AC13,Z18)/8,"")</f>
+      <c r="W21" s="62"/>
+      <c r="X21" s="62"/>
+      <c r="Y21" s="62"/>
+      <c r="Z21" s="62" t="str">
+        <f t="shared" ref="Z21" si="4">IF(SUM(Z7:AC13,Z18)/8 &gt; 0,SUM(Z7:AC13,Z18)/8,"")</f>
         <v/>
       </c>
-      <c r="AA21" s="60"/>
-      <c r="AB21" s="60"/>
-      <c r="AC21" s="60"/>
-      <c r="AD21" s="55"/>
-      <c r="AE21" s="56"/>
-      <c r="AF21" s="56"/>
-      <c r="AG21" s="56"/>
-      <c r="AH21" s="56"/>
-      <c r="AI21" s="57"/>
-      <c r="AJ21" s="21"/>
-      <c r="AK21" s="22"/>
-      <c r="AL21" s="22"/>
-      <c r="AM21" s="22"/>
-      <c r="AN21" s="23"/>
+      <c r="AA21" s="62"/>
+      <c r="AB21" s="62"/>
+      <c r="AC21" s="62"/>
+      <c r="AD21" s="57"/>
+      <c r="AE21" s="58"/>
+      <c r="AF21" s="58"/>
+      <c r="AG21" s="58"/>
+      <c r="AH21" s="58"/>
+      <c r="AI21" s="59"/>
+      <c r="AJ21" s="17"/>
+      <c r="AK21" s="18"/>
+      <c r="AL21" s="18"/>
+      <c r="AM21" s="18"/>
+      <c r="AN21" s="19"/>
     </row>
     <row r="22" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6"/>
       <c r="B22" s="7"/>
-      <c r="C22" s="59" t="s">
+      <c r="C22" s="61" t="s">
         <v>26</v>
       </c>
-      <c r="D22" s="59"/>
-      <c r="E22" s="59"/>
-      <c r="F22" s="59"/>
-      <c r="G22" s="59"/>
-      <c r="H22" s="59"/>
-      <c r="I22" s="59"/>
-      <c r="J22" s="59"/>
-      <c r="K22" s="59"/>
-      <c r="L22" s="59"/>
-      <c r="M22" s="61"/>
-      <c r="N22" s="70" t="s">
+      <c r="D22" s="61"/>
+      <c r="E22" s="61"/>
+      <c r="F22" s="61"/>
+      <c r="G22" s="61"/>
+      <c r="H22" s="61"/>
+      <c r="I22" s="61"/>
+      <c r="J22" s="61"/>
+      <c r="K22" s="61"/>
+      <c r="L22" s="61"/>
+      <c r="M22" s="63"/>
+      <c r="N22" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="O22" s="71"/>
-      <c r="P22" s="71"/>
-      <c r="Q22" s="71"/>
-      <c r="R22" s="71"/>
-      <c r="S22" s="71"/>
-      <c r="T22" s="71"/>
-      <c r="U22" s="71"/>
-      <c r="V22" s="71"/>
-      <c r="W22" s="71"/>
-      <c r="X22" s="71"/>
-      <c r="Y22" s="71"/>
-      <c r="Z22" s="71"/>
-      <c r="AA22" s="71"/>
-      <c r="AB22" s="71"/>
-      <c r="AC22" s="72"/>
-      <c r="AD22" s="67" t="str">
+      <c r="O22" s="73"/>
+      <c r="P22" s="73"/>
+      <c r="Q22" s="73"/>
+      <c r="R22" s="73"/>
+      <c r="S22" s="73"/>
+      <c r="T22" s="73"/>
+      <c r="U22" s="73"/>
+      <c r="V22" s="73"/>
+      <c r="W22" s="73"/>
+      <c r="X22" s="73"/>
+      <c r="Y22" s="73"/>
+      <c r="Z22" s="73"/>
+      <c r="AA22" s="73"/>
+      <c r="AB22" s="73"/>
+      <c r="AC22" s="74"/>
+      <c r="AD22" s="69" t="str">
         <f>IF(COUNT(AD7:AI13,AD18)=8,SUM(AD7:AI13,AD18)/8,"")</f>
         <v/>
       </c>
-      <c r="AE22" s="68"/>
-      <c r="AF22" s="68"/>
-      <c r="AG22" s="68"/>
-      <c r="AH22" s="68"/>
-      <c r="AI22" s="69"/>
+      <c r="AE22" s="70"/>
+      <c r="AF22" s="70"/>
+      <c r="AG22" s="70"/>
+      <c r="AH22" s="70"/>
+      <c r="AI22" s="71"/>
       <c r="AJ22" s="4"/>
       <c r="AK22" s="4"/>
       <c r="AL22" s="4"/>
@@ -2134,629 +2138,629 @@
       <c r="Y24" s="2"/>
     </row>
     <row r="25" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="50" t="s">
+      <c r="A25" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="50"/>
-      <c r="C25" s="50"/>
-      <c r="D25" s="50"/>
-      <c r="E25" s="50"/>
-      <c r="F25" s="50"/>
-      <c r="G25" s="50"/>
-      <c r="H25" s="50"/>
-      <c r="I25" s="50"/>
-      <c r="J25" s="50"/>
-      <c r="K25" s="50"/>
-      <c r="L25" s="50"/>
-      <c r="M25" s="50"/>
-      <c r="N25" s="50"/>
-      <c r="O25" s="50"/>
-      <c r="P25" s="27" t="s">
+      <c r="B25" s="52"/>
+      <c r="C25" s="52"/>
+      <c r="D25" s="52"/>
+      <c r="E25" s="52"/>
+      <c r="F25" s="52"/>
+      <c r="G25" s="52"/>
+      <c r="H25" s="52"/>
+      <c r="I25" s="52"/>
+      <c r="J25" s="52"/>
+      <c r="K25" s="52"/>
+      <c r="L25" s="52"/>
+      <c r="M25" s="52"/>
+      <c r="N25" s="52"/>
+      <c r="O25" s="52"/>
+      <c r="P25" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="Q25" s="27"/>
-      <c r="R25" s="27" t="s">
+      <c r="Q25" s="28"/>
+      <c r="R25" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="S25" s="27"/>
-      <c r="T25" s="27" t="s">
+      <c r="S25" s="28"/>
+      <c r="T25" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="U25" s="27"/>
-      <c r="V25" s="27" t="s">
+      <c r="U25" s="28"/>
+      <c r="V25" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="W25" s="27"/>
-      <c r="Y25" s="62" t="s">
+      <c r="W25" s="28"/>
+      <c r="Y25" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="Z25" s="62"/>
-      <c r="AA25" s="62"/>
-      <c r="AB25" s="62"/>
-      <c r="AC25" s="62"/>
-      <c r="AD25" s="62"/>
-      <c r="AE25" s="62"/>
-      <c r="AF25" s="62"/>
-      <c r="AG25" s="62"/>
-      <c r="AH25" s="62"/>
-      <c r="AI25" s="62"/>
-      <c r="AJ25" s="62"/>
+      <c r="Z25" s="64"/>
+      <c r="AA25" s="64"/>
+      <c r="AB25" s="64"/>
+      <c r="AC25" s="64"/>
+      <c r="AD25" s="64"/>
+      <c r="AE25" s="64"/>
+      <c r="AF25" s="64"/>
+      <c r="AG25" s="64"/>
+      <c r="AH25" s="64"/>
+      <c r="AI25" s="64"/>
+      <c r="AJ25" s="64"/>
       <c r="AK25" s="3"/>
       <c r="AL25" s="3"/>
       <c r="AM25" s="3"/>
       <c r="AN25" s="3"/>
     </row>
     <row r="26" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="28" t="s">
+      <c r="A26" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="28"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="28"/>
-      <c r="J26" s="28"/>
-      <c r="K26" s="28"/>
-      <c r="L26" s="28"/>
-      <c r="M26" s="28"/>
-      <c r="N26" s="28"/>
-      <c r="O26" s="28"/>
-      <c r="P26" s="19"/>
-      <c r="Q26" s="19"/>
-      <c r="R26" s="19"/>
-      <c r="S26" s="19"/>
-      <c r="T26" s="19"/>
-      <c r="U26" s="19"/>
-      <c r="V26" s="20"/>
-      <c r="W26" s="20"/>
-      <c r="Y26" s="29" t="s">
+      <c r="B26" s="29"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="29"/>
+      <c r="H26" s="29"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="29"/>
+      <c r="K26" s="29"/>
+      <c r="L26" s="29"/>
+      <c r="M26" s="29"/>
+      <c r="N26" s="29"/>
+      <c r="O26" s="29"/>
+      <c r="P26" s="22"/>
+      <c r="Q26" s="22"/>
+      <c r="R26" s="22"/>
+      <c r="S26" s="22"/>
+      <c r="T26" s="22"/>
+      <c r="U26" s="22"/>
+      <c r="V26" s="23"/>
+      <c r="W26" s="23"/>
+      <c r="Y26" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="Z26" s="29"/>
-      <c r="AA26" s="29"/>
-      <c r="AB26" s="29"/>
-      <c r="AC26" s="29"/>
-      <c r="AD26" s="29"/>
-      <c r="AE26" s="29"/>
-      <c r="AF26" s="29"/>
-      <c r="AG26" s="29"/>
-      <c r="AH26" s="29"/>
-      <c r="AI26" s="29"/>
-      <c r="AJ26" s="29"/>
-      <c r="AK26" s="29"/>
-      <c r="AL26" s="29"/>
-      <c r="AM26" s="29"/>
+      <c r="Z26" s="31"/>
+      <c r="AA26" s="31"/>
+      <c r="AB26" s="31"/>
+      <c r="AC26" s="31"/>
+      <c r="AD26" s="31"/>
+      <c r="AE26" s="31"/>
+      <c r="AF26" s="31"/>
+      <c r="AG26" s="31"/>
+      <c r="AH26" s="31"/>
+      <c r="AI26" s="31"/>
+      <c r="AJ26" s="31"/>
+      <c r="AK26" s="31"/>
+      <c r="AL26" s="31"/>
+      <c r="AM26" s="31"/>
       <c r="AN26" s="3">
         <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="28" t="s">
+      <c r="A27" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="28"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="28"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="28"/>
-      <c r="J27" s="28"/>
-      <c r="K27" s="28"/>
-      <c r="L27" s="28"/>
-      <c r="M27" s="28"/>
-      <c r="N27" s="28"/>
-      <c r="O27" s="28"/>
-      <c r="P27" s="19"/>
-      <c r="Q27" s="19"/>
-      <c r="R27" s="19"/>
-      <c r="S27" s="19"/>
-      <c r="T27" s="19"/>
-      <c r="U27" s="19"/>
-      <c r="V27" s="20"/>
-      <c r="W27" s="20"/>
-      <c r="Y27" s="29" t="s">
+      <c r="B27" s="29"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29"/>
+      <c r="I27" s="29"/>
+      <c r="J27" s="29"/>
+      <c r="K27" s="29"/>
+      <c r="L27" s="29"/>
+      <c r="M27" s="29"/>
+      <c r="N27" s="29"/>
+      <c r="O27" s="29"/>
+      <c r="P27" s="22"/>
+      <c r="Q27" s="22"/>
+      <c r="R27" s="22"/>
+      <c r="S27" s="22"/>
+      <c r="T27" s="22"/>
+      <c r="U27" s="22"/>
+      <c r="V27" s="23"/>
+      <c r="W27" s="23"/>
+      <c r="Y27" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="Z27" s="29"/>
-      <c r="AA27" s="29"/>
-      <c r="AB27" s="29"/>
-      <c r="AC27" s="29"/>
-      <c r="AD27" s="29"/>
-      <c r="AE27" s="29"/>
-      <c r="AF27" s="29"/>
-      <c r="AG27" s="29"/>
-      <c r="AH27" s="29"/>
-      <c r="AI27" s="29"/>
-      <c r="AJ27" s="29"/>
-      <c r="AK27" s="29"/>
-      <c r="AL27" s="29"/>
-      <c r="AM27" s="29"/>
+      <c r="Z27" s="31"/>
+      <c r="AA27" s="31"/>
+      <c r="AB27" s="31"/>
+      <c r="AC27" s="31"/>
+      <c r="AD27" s="31"/>
+      <c r="AE27" s="31"/>
+      <c r="AF27" s="31"/>
+      <c r="AG27" s="31"/>
+      <c r="AH27" s="31"/>
+      <c r="AI27" s="31"/>
+      <c r="AJ27" s="31"/>
+      <c r="AK27" s="31"/>
+      <c r="AL27" s="31"/>
+      <c r="AM27" s="31"/>
       <c r="AN27" s="3">
         <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="28" t="s">
+      <c r="A28" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="28"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="28"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="28"/>
-      <c r="J28" s="28"/>
-      <c r="K28" s="28"/>
-      <c r="L28" s="28"/>
-      <c r="M28" s="28"/>
-      <c r="N28" s="28"/>
-      <c r="O28" s="28"/>
-      <c r="P28" s="19"/>
-      <c r="Q28" s="19"/>
-      <c r="R28" s="19"/>
-      <c r="S28" s="19"/>
-      <c r="T28" s="19"/>
-      <c r="U28" s="19"/>
-      <c r="V28" s="20"/>
-      <c r="W28" s="20"/>
-      <c r="Y28" s="29" t="s">
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="29"/>
+      <c r="J28" s="29"/>
+      <c r="K28" s="29"/>
+      <c r="L28" s="29"/>
+      <c r="M28" s="29"/>
+      <c r="N28" s="29"/>
+      <c r="O28" s="29"/>
+      <c r="P28" s="22"/>
+      <c r="Q28" s="22"/>
+      <c r="R28" s="22"/>
+      <c r="S28" s="22"/>
+      <c r="T28" s="22"/>
+      <c r="U28" s="22"/>
+      <c r="V28" s="23"/>
+      <c r="W28" s="23"/>
+      <c r="Y28" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="Z28" s="29"/>
-      <c r="AA28" s="29"/>
-      <c r="AB28" s="29"/>
-      <c r="AC28" s="29"/>
-      <c r="AD28" s="29"/>
-      <c r="AE28" s="29"/>
-      <c r="AF28" s="29"/>
-      <c r="AG28" s="29"/>
-      <c r="AH28" s="29"/>
-      <c r="AI28" s="29"/>
-      <c r="AJ28" s="29"/>
-      <c r="AK28" s="29"/>
-      <c r="AL28" s="29"/>
-      <c r="AM28" s="29"/>
+      <c r="Z28" s="31"/>
+      <c r="AA28" s="31"/>
+      <c r="AB28" s="31"/>
+      <c r="AC28" s="31"/>
+      <c r="AD28" s="31"/>
+      <c r="AE28" s="31"/>
+      <c r="AF28" s="31"/>
+      <c r="AG28" s="31"/>
+      <c r="AH28" s="31"/>
+      <c r="AI28" s="31"/>
+      <c r="AJ28" s="31"/>
+      <c r="AK28" s="31"/>
+      <c r="AL28" s="31"/>
+      <c r="AM28" s="31"/>
       <c r="AN28" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="28" t="s">
+      <c r="A29" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="28"/>
-      <c r="J29" s="28"/>
-      <c r="K29" s="28"/>
-      <c r="L29" s="28"/>
-      <c r="M29" s="28"/>
-      <c r="N29" s="28"/>
-      <c r="O29" s="28"/>
-      <c r="P29" s="19"/>
-      <c r="Q29" s="19"/>
-      <c r="R29" s="19"/>
-      <c r="S29" s="19"/>
-      <c r="T29" s="19"/>
-      <c r="U29" s="19"/>
-      <c r="V29" s="20"/>
-      <c r="W29" s="20"/>
-      <c r="Y29" s="29" t="s">
+      <c r="B29" s="29"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="29"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="29"/>
+      <c r="K29" s="29"/>
+      <c r="L29" s="29"/>
+      <c r="M29" s="29"/>
+      <c r="N29" s="29"/>
+      <c r="O29" s="29"/>
+      <c r="P29" s="22"/>
+      <c r="Q29" s="22"/>
+      <c r="R29" s="22"/>
+      <c r="S29" s="22"/>
+      <c r="T29" s="22"/>
+      <c r="U29" s="22"/>
+      <c r="V29" s="23"/>
+      <c r="W29" s="23"/>
+      <c r="Y29" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="Z29" s="29"/>
-      <c r="AA29" s="29"/>
-      <c r="AB29" s="29"/>
-      <c r="AC29" s="29"/>
-      <c r="AD29" s="29"/>
-      <c r="AE29" s="29"/>
-      <c r="AF29" s="29"/>
-      <c r="AG29" s="29"/>
-      <c r="AH29" s="29"/>
-      <c r="AI29" s="29"/>
-      <c r="AJ29" s="29"/>
-      <c r="AK29" s="29"/>
-      <c r="AL29" s="29"/>
-      <c r="AM29" s="29"/>
+      <c r="Z29" s="31"/>
+      <c r="AA29" s="31"/>
+      <c r="AB29" s="31"/>
+      <c r="AC29" s="31"/>
+      <c r="AD29" s="31"/>
+      <c r="AE29" s="31"/>
+      <c r="AF29" s="31"/>
+      <c r="AG29" s="31"/>
+      <c r="AH29" s="31"/>
+      <c r="AI29" s="31"/>
+      <c r="AJ29" s="31"/>
+      <c r="AK29" s="31"/>
+      <c r="AL29" s="31"/>
+      <c r="AM29" s="31"/>
       <c r="AN29" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="28" t="s">
+      <c r="A30" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="28"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="28"/>
-      <c r="H30" s="28"/>
-      <c r="I30" s="28"/>
-      <c r="J30" s="28"/>
-      <c r="K30" s="28"/>
-      <c r="L30" s="28"/>
-      <c r="M30" s="28"/>
-      <c r="N30" s="28"/>
-      <c r="O30" s="28"/>
-      <c r="P30" s="19"/>
-      <c r="Q30" s="19"/>
-      <c r="R30" s="19"/>
-      <c r="S30" s="19"/>
-      <c r="T30" s="19"/>
-      <c r="U30" s="19"/>
-      <c r="V30" s="20"/>
-      <c r="W30" s="20"/>
-      <c r="Y30" s="29" t="s">
+      <c r="B30" s="29"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="29"/>
+      <c r="I30" s="29"/>
+      <c r="J30" s="29"/>
+      <c r="K30" s="29"/>
+      <c r="L30" s="29"/>
+      <c r="M30" s="29"/>
+      <c r="N30" s="29"/>
+      <c r="O30" s="29"/>
+      <c r="P30" s="22"/>
+      <c r="Q30" s="22"/>
+      <c r="R30" s="22"/>
+      <c r="S30" s="22"/>
+      <c r="T30" s="22"/>
+      <c r="U30" s="22"/>
+      <c r="V30" s="23"/>
+      <c r="W30" s="23"/>
+      <c r="Y30" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="Z30" s="29"/>
-      <c r="AA30" s="29"/>
-      <c r="AB30" s="29"/>
-      <c r="AC30" s="29"/>
-      <c r="AD30" s="29"/>
-      <c r="AE30" s="29"/>
-      <c r="AF30" s="29"/>
-      <c r="AG30" s="29"/>
-      <c r="AH30" s="29"/>
-      <c r="AI30" s="29"/>
-      <c r="AJ30" s="29"/>
-      <c r="AK30" s="29"/>
-      <c r="AL30" s="29"/>
-      <c r="AM30" s="29"/>
+      <c r="Z30" s="31"/>
+      <c r="AA30" s="31"/>
+      <c r="AB30" s="31"/>
+      <c r="AC30" s="31"/>
+      <c r="AD30" s="31"/>
+      <c r="AE30" s="31"/>
+      <c r="AF30" s="31"/>
+      <c r="AG30" s="31"/>
+      <c r="AH30" s="31"/>
+      <c r="AI30" s="31"/>
+      <c r="AJ30" s="31"/>
+      <c r="AK30" s="31"/>
+      <c r="AL30" s="31"/>
+      <c r="AM30" s="31"/>
       <c r="AN30" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="28" t="s">
+      <c r="A31" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="28"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="28"/>
-      <c r="H31" s="28"/>
-      <c r="I31" s="28"/>
-      <c r="J31" s="28"/>
-      <c r="K31" s="28"/>
-      <c r="L31" s="28"/>
-      <c r="M31" s="28"/>
-      <c r="N31" s="28"/>
-      <c r="O31" s="28"/>
-      <c r="P31" s="19"/>
-      <c r="Q31" s="19"/>
-      <c r="R31" s="19"/>
-      <c r="S31" s="19"/>
-      <c r="T31" s="19"/>
-      <c r="U31" s="19"/>
-      <c r="V31" s="20"/>
-      <c r="W31" s="20"/>
+      <c r="B31" s="29"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="29"/>
+      <c r="I31" s="29"/>
+      <c r="J31" s="29"/>
+      <c r="K31" s="29"/>
+      <c r="L31" s="29"/>
+      <c r="M31" s="29"/>
+      <c r="N31" s="29"/>
+      <c r="O31" s="29"/>
+      <c r="P31" s="22"/>
+      <c r="Q31" s="22"/>
+      <c r="R31" s="22"/>
+      <c r="S31" s="22"/>
+      <c r="T31" s="22"/>
+      <c r="U31" s="22"/>
+      <c r="V31" s="23"/>
+      <c r="W31" s="23"/>
       <c r="X31" s="3"/>
-      <c r="Y31" s="29" t="s">
+      <c r="Y31" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="Z31" s="29"/>
-      <c r="AA31" s="29"/>
-      <c r="AB31" s="29"/>
-      <c r="AC31" s="29"/>
-      <c r="AD31" s="29"/>
-      <c r="AE31" s="29"/>
-      <c r="AF31" s="29"/>
-      <c r="AG31" s="29"/>
-      <c r="AH31" s="29"/>
-      <c r="AI31" s="29"/>
-      <c r="AJ31" s="29"/>
-      <c r="AK31" s="29"/>
-      <c r="AL31" s="29"/>
-      <c r="AM31" s="29"/>
+      <c r="Z31" s="31"/>
+      <c r="AA31" s="31"/>
+      <c r="AB31" s="31"/>
+      <c r="AC31" s="31"/>
+      <c r="AD31" s="31"/>
+      <c r="AE31" s="31"/>
+      <c r="AF31" s="31"/>
+      <c r="AG31" s="31"/>
+      <c r="AH31" s="31"/>
+      <c r="AI31" s="31"/>
+      <c r="AJ31" s="31"/>
+      <c r="AK31" s="31"/>
+      <c r="AL31" s="31"/>
+      <c r="AM31" s="31"/>
       <c r="AN31" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="28" t="s">
+      <c r="A32" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="28"/>
-      <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
-      <c r="N32" s="28"/>
-      <c r="O32" s="28"/>
-      <c r="P32" s="19"/>
-      <c r="Q32" s="19"/>
-      <c r="R32" s="19"/>
-      <c r="S32" s="19"/>
-      <c r="T32" s="19"/>
-      <c r="U32" s="19"/>
-      <c r="V32" s="20"/>
-      <c r="W32" s="20"/>
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="29"/>
+      <c r="K32" s="29"/>
+      <c r="L32" s="29"/>
+      <c r="M32" s="29"/>
+      <c r="N32" s="29"/>
+      <c r="O32" s="29"/>
+      <c r="P32" s="22"/>
+      <c r="Q32" s="22"/>
+      <c r="R32" s="22"/>
+      <c r="S32" s="22"/>
+      <c r="T32" s="22"/>
+      <c r="U32" s="22"/>
+      <c r="V32" s="23"/>
+      <c r="W32" s="23"/>
       <c r="X32" s="3"/>
     </row>
     <row r="33" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="28" t="s">
+      <c r="A33" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="28"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="28"/>
-      <c r="H33" s="28"/>
-      <c r="I33" s="28"/>
-      <c r="J33" s="28"/>
-      <c r="K33" s="28"/>
-      <c r="L33" s="28"/>
-      <c r="M33" s="28"/>
-      <c r="N33" s="28"/>
-      <c r="O33" s="28"/>
-      <c r="P33" s="19"/>
-      <c r="Q33" s="19"/>
-      <c r="R33" s="19"/>
-      <c r="S33" s="19"/>
-      <c r="T33" s="19"/>
-      <c r="U33" s="19"/>
-      <c r="V33" s="20"/>
-      <c r="W33" s="20"/>
+      <c r="B33" s="29"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="29"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="29"/>
+      <c r="H33" s="29"/>
+      <c r="I33" s="29"/>
+      <c r="J33" s="29"/>
+      <c r="K33" s="29"/>
+      <c r="L33" s="29"/>
+      <c r="M33" s="29"/>
+      <c r="N33" s="29"/>
+      <c r="O33" s="29"/>
+      <c r="P33" s="22"/>
+      <c r="Q33" s="22"/>
+      <c r="R33" s="22"/>
+      <c r="S33" s="22"/>
+      <c r="T33" s="22"/>
+      <c r="U33" s="22"/>
+      <c r="V33" s="23"/>
+      <c r="W33" s="23"/>
       <c r="X33" s="3"/>
     </row>
     <row r="34" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="28" t="s">
+      <c r="A34" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="28"/>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="28"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="28"/>
-      <c r="H34" s="28"/>
-      <c r="I34" s="28"/>
-      <c r="J34" s="28"/>
-      <c r="K34" s="28"/>
-      <c r="L34" s="28"/>
-      <c r="M34" s="28"/>
-      <c r="N34" s="28"/>
-      <c r="O34" s="28"/>
-      <c r="P34" s="19"/>
-      <c r="Q34" s="19"/>
-      <c r="R34" s="19"/>
-      <c r="S34" s="19"/>
-      <c r="T34" s="19"/>
-      <c r="U34" s="19"/>
-      <c r="V34" s="20"/>
-      <c r="W34" s="20"/>
+      <c r="B34" s="29"/>
+      <c r="C34" s="29"/>
+      <c r="D34" s="29"/>
+      <c r="E34" s="29"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="29"/>
+      <c r="H34" s="29"/>
+      <c r="I34" s="29"/>
+      <c r="J34" s="29"/>
+      <c r="K34" s="29"/>
+      <c r="L34" s="29"/>
+      <c r="M34" s="29"/>
+      <c r="N34" s="29"/>
+      <c r="O34" s="29"/>
+      <c r="P34" s="22"/>
+      <c r="Q34" s="22"/>
+      <c r="R34" s="22"/>
+      <c r="S34" s="22"/>
+      <c r="T34" s="22"/>
+      <c r="U34" s="22"/>
+      <c r="V34" s="23"/>
+      <c r="W34" s="23"/>
       <c r="X34" s="3"/>
     </row>
     <row r="35" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="28" t="s">
+      <c r="A35" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="28"/>
-      <c r="C35" s="28"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="28"/>
-      <c r="F35" s="28"/>
-      <c r="G35" s="28"/>
-      <c r="H35" s="28"/>
-      <c r="I35" s="28"/>
-      <c r="J35" s="28"/>
-      <c r="K35" s="28"/>
-      <c r="L35" s="28"/>
-      <c r="M35" s="28"/>
-      <c r="N35" s="28"/>
-      <c r="O35" s="28"/>
-      <c r="P35" s="19"/>
-      <c r="Q35" s="19"/>
-      <c r="R35" s="19"/>
-      <c r="S35" s="19"/>
-      <c r="T35" s="19"/>
-      <c r="U35" s="19"/>
-      <c r="V35" s="20"/>
-      <c r="W35" s="20"/>
+      <c r="B35" s="29"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="29"/>
+      <c r="F35" s="29"/>
+      <c r="G35" s="29"/>
+      <c r="H35" s="29"/>
+      <c r="I35" s="29"/>
+      <c r="J35" s="29"/>
+      <c r="K35" s="29"/>
+      <c r="L35" s="29"/>
+      <c r="M35" s="29"/>
+      <c r="N35" s="29"/>
+      <c r="O35" s="29"/>
+      <c r="P35" s="22"/>
+      <c r="Q35" s="22"/>
+      <c r="R35" s="22"/>
+      <c r="S35" s="22"/>
+      <c r="T35" s="22"/>
+      <c r="U35" s="22"/>
+      <c r="V35" s="23"/>
+      <c r="W35" s="23"/>
       <c r="X35" s="3"/>
     </row>
     <row r="36" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="28" t="s">
+      <c r="A36" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="28"/>
-      <c r="C36" s="28"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="28"/>
-      <c r="F36" s="28"/>
-      <c r="G36" s="28"/>
-      <c r="H36" s="28"/>
-      <c r="I36" s="28"/>
-      <c r="J36" s="28"/>
-      <c r="K36" s="28"/>
-      <c r="L36" s="28"/>
-      <c r="M36" s="28"/>
-      <c r="N36" s="28"/>
-      <c r="O36" s="28"/>
-      <c r="P36" s="19"/>
-      <c r="Q36" s="19"/>
-      <c r="R36" s="19"/>
-      <c r="S36" s="19"/>
-      <c r="T36" s="19"/>
-      <c r="U36" s="19"/>
-      <c r="V36" s="20"/>
-      <c r="W36" s="20"/>
+      <c r="B36" s="29"/>
+      <c r="C36" s="29"/>
+      <c r="D36" s="29"/>
+      <c r="E36" s="29"/>
+      <c r="F36" s="29"/>
+      <c r="G36" s="29"/>
+      <c r="H36" s="29"/>
+      <c r="I36" s="29"/>
+      <c r="J36" s="29"/>
+      <c r="K36" s="29"/>
+      <c r="L36" s="29"/>
+      <c r="M36" s="29"/>
+      <c r="N36" s="29"/>
+      <c r="O36" s="29"/>
+      <c r="P36" s="22"/>
+      <c r="Q36" s="22"/>
+      <c r="R36" s="22"/>
+      <c r="S36" s="22"/>
+      <c r="T36" s="22"/>
+      <c r="U36" s="22"/>
+      <c r="V36" s="23"/>
+      <c r="W36" s="23"/>
       <c r="X36" s="3"/>
     </row>
     <row r="37" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="28" t="s">
+      <c r="A37" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="28"/>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
-      <c r="H37" s="28"/>
-      <c r="I37" s="28"/>
-      <c r="J37" s="28"/>
-      <c r="K37" s="28"/>
-      <c r="L37" s="28"/>
-      <c r="M37" s="28"/>
-      <c r="N37" s="28"/>
-      <c r="O37" s="28"/>
-      <c r="P37" s="19"/>
-      <c r="Q37" s="19"/>
-      <c r="R37" s="19"/>
-      <c r="S37" s="19"/>
-      <c r="T37" s="19"/>
-      <c r="U37" s="19"/>
-      <c r="V37" s="20"/>
-      <c r="W37" s="20"/>
+      <c r="B37" s="29"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="29"/>
+      <c r="H37" s="29"/>
+      <c r="I37" s="29"/>
+      <c r="J37" s="29"/>
+      <c r="K37" s="29"/>
+      <c r="L37" s="29"/>
+      <c r="M37" s="29"/>
+      <c r="N37" s="29"/>
+      <c r="O37" s="29"/>
+      <c r="P37" s="22"/>
+      <c r="Q37" s="22"/>
+      <c r="R37" s="22"/>
+      <c r="S37" s="22"/>
+      <c r="T37" s="22"/>
+      <c r="U37" s="22"/>
+      <c r="V37" s="23"/>
+      <c r="W37" s="23"/>
       <c r="X37" s="3"/>
-      <c r="AC37" s="58" t="s">
+      <c r="AC37" s="60" t="s">
         <v>55</v>
       </c>
-      <c r="AD37" s="58"/>
-      <c r="AE37" s="58"/>
-      <c r="AF37" s="58"/>
-      <c r="AG37" s="58"/>
-      <c r="AH37" s="58"/>
-      <c r="AI37" s="58"/>
-      <c r="AJ37" s="58"/>
-      <c r="AK37" s="58"/>
-      <c r="AL37" s="58"/>
-      <c r="AM37" s="58"/>
+      <c r="AD37" s="60"/>
+      <c r="AE37" s="60"/>
+      <c r="AF37" s="60"/>
+      <c r="AG37" s="60"/>
+      <c r="AH37" s="60"/>
+      <c r="AI37" s="60"/>
+      <c r="AJ37" s="60"/>
+      <c r="AK37" s="60"/>
+      <c r="AL37" s="60"/>
+      <c r="AM37" s="60"/>
     </row>
     <row r="38" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="66" t="s">
+      <c r="A38" s="68" t="s">
         <v>41</v>
       </c>
-      <c r="B38" s="66"/>
-      <c r="C38" s="66"/>
-      <c r="D38" s="66"/>
-      <c r="E38" s="66"/>
-      <c r="F38" s="66"/>
-      <c r="G38" s="66"/>
-      <c r="H38" s="66"/>
-      <c r="I38" s="66"/>
-      <c r="J38" s="66"/>
-      <c r="K38" s="66"/>
-      <c r="L38" s="66"/>
-      <c r="M38" s="66"/>
-      <c r="N38" s="66"/>
-      <c r="O38" s="66"/>
-      <c r="P38" s="20">
+      <c r="B38" s="68"/>
+      <c r="C38" s="68"/>
+      <c r="D38" s="68"/>
+      <c r="E38" s="68"/>
+      <c r="F38" s="68"/>
+      <c r="G38" s="68"/>
+      <c r="H38" s="68"/>
+      <c r="I38" s="68"/>
+      <c r="J38" s="68"/>
+      <c r="K38" s="68"/>
+      <c r="L38" s="68"/>
+      <c r="M38" s="68"/>
+      <c r="N38" s="68"/>
+      <c r="O38" s="68"/>
+      <c r="P38" s="23">
         <f>SUM(P26:Q37)/12</f>
         <v>0</v>
       </c>
-      <c r="Q38" s="20"/>
-      <c r="R38" s="20">
-        <f t="shared" ref="R38:V38" si="6">SUM(R26:S37)/12</f>
+      <c r="Q38" s="23"/>
+      <c r="R38" s="23">
+        <f t="shared" ref="R38:V38" si="5">SUM(R26:S37)/12</f>
         <v>0</v>
       </c>
-      <c r="S38" s="20"/>
-      <c r="T38" s="20">
-        <f t="shared" si="6"/>
+      <c r="S38" s="23"/>
+      <c r="T38" s="23">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U38" s="20"/>
-      <c r="V38" s="20">
-        <f t="shared" si="6"/>
+      <c r="U38" s="23"/>
+      <c r="V38" s="23">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="W38" s="20"/>
+      <c r="W38" s="23"/>
       <c r="X38" s="3"/>
       <c r="AD38" s="2"/>
       <c r="AE38" s="2"/>
-      <c r="AF38" s="64" t="s">
+      <c r="AF38" s="66" t="s">
         <v>56</v>
       </c>
-      <c r="AG38" s="64"/>
-      <c r="AH38" s="64"/>
-      <c r="AI38" s="64"/>
-      <c r="AJ38" s="64"/>
-      <c r="AK38" s="64"/>
+      <c r="AG38" s="66"/>
+      <c r="AH38" s="66"/>
+      <c r="AI38" s="66"/>
+      <c r="AJ38" s="66"/>
+      <c r="AK38" s="66"/>
       <c r="AL38" s="3"/>
       <c r="AM38" s="3"/>
     </row>
     <row r="39" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="54" t="s">
+      <c r="A39" s="56" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="54"/>
-      <c r="C39" s="54"/>
-      <c r="D39" s="54"/>
-      <c r="E39" s="54"/>
-      <c r="F39" s="54"/>
-      <c r="G39" s="52" t="s">
+      <c r="B39" s="56"/>
+      <c r="C39" s="56"/>
+      <c r="D39" s="56"/>
+      <c r="E39" s="56"/>
+      <c r="F39" s="56"/>
+      <c r="G39" s="54" t="s">
         <v>46</v>
       </c>
-      <c r="H39" s="52"/>
-      <c r="I39" s="52" t="s">
+      <c r="H39" s="54"/>
+      <c r="I39" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="J39" s="52"/>
-      <c r="K39" s="52" t="s">
+      <c r="J39" s="54"/>
+      <c r="K39" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="L39" s="52"/>
-      <c r="M39" s="52" t="s">
+      <c r="L39" s="54"/>
+      <c r="M39" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="N39" s="52"/>
-      <c r="O39" s="52" t="s">
+      <c r="N39" s="54"/>
+      <c r="O39" s="54" t="s">
         <v>50</v>
       </c>
-      <c r="P39" s="52"/>
-      <c r="Q39" s="52" t="s">
+      <c r="P39" s="54"/>
+      <c r="Q39" s="54" t="s">
         <v>51</v>
       </c>
-      <c r="R39" s="52"/>
-      <c r="S39" s="52" t="s">
+      <c r="R39" s="54"/>
+      <c r="S39" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="T39" s="52"/>
-      <c r="U39" s="52" t="s">
+      <c r="T39" s="54"/>
+      <c r="U39" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="V39" s="52"/>
-      <c r="W39" s="52" t="s">
+      <c r="V39" s="54"/>
+      <c r="W39" s="54" t="s">
         <v>66</v>
       </c>
-      <c r="X39" s="52"/>
-      <c r="Y39" s="52" t="s">
+      <c r="X39" s="54"/>
+      <c r="Y39" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="Z39" s="52"/>
-      <c r="AA39" s="52" t="s">
+      <c r="Z39" s="54"/>
+      <c r="AA39" s="54" t="s">
         <v>54</v>
       </c>
-      <c r="AB39" s="52"/>
-      <c r="AC39" s="54"/>
-      <c r="AD39" s="54"/>
+      <c r="AB39" s="54"/>
+      <c r="AC39" s="56"/>
+      <c r="AD39" s="56"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
@@ -2767,61 +2771,61 @@
       <c r="AN39" s="3"/>
     </row>
     <row r="40" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="51" t="s">
+      <c r="A40" s="53" t="s">
         <v>43</v>
       </c>
-      <c r="B40" s="51"/>
-      <c r="C40" s="51"/>
-      <c r="D40" s="51"/>
-      <c r="E40" s="51"/>
-      <c r="F40" s="51"/>
-      <c r="G40" s="19">
+      <c r="B40" s="53"/>
+      <c r="C40" s="53"/>
+      <c r="D40" s="53"/>
+      <c r="E40" s="53"/>
+      <c r="F40" s="53"/>
+      <c r="G40" s="22">
         <v>18</v>
       </c>
-      <c r="H40" s="19"/>
-      <c r="I40" s="19">
+      <c r="H40" s="22"/>
+      <c r="I40" s="22">
         <v>23</v>
       </c>
-      <c r="J40" s="19"/>
-      <c r="K40" s="19">
+      <c r="J40" s="22"/>
+      <c r="K40" s="22">
         <v>22</v>
       </c>
-      <c r="L40" s="19"/>
-      <c r="M40" s="19">
+      <c r="L40" s="22"/>
+      <c r="M40" s="22">
         <v>19</v>
       </c>
-      <c r="N40" s="19"/>
-      <c r="O40" s="19">
+      <c r="N40" s="22"/>
+      <c r="O40" s="22">
         <v>16</v>
       </c>
-      <c r="P40" s="19"/>
-      <c r="Q40" s="19">
+      <c r="P40" s="22"/>
+      <c r="Q40" s="22">
         <v>22</v>
       </c>
-      <c r="R40" s="19"/>
-      <c r="S40" s="19">
+      <c r="R40" s="22"/>
+      <c r="S40" s="22">
         <v>22</v>
       </c>
-      <c r="T40" s="19"/>
-      <c r="U40" s="19">
+      <c r="T40" s="22"/>
+      <c r="U40" s="22">
         <v>20</v>
       </c>
-      <c r="V40" s="19"/>
-      <c r="W40" s="19">
+      <c r="V40" s="22"/>
+      <c r="W40" s="22">
         <v>22</v>
       </c>
-      <c r="X40" s="19"/>
-      <c r="Y40" s="19">
+      <c r="X40" s="22"/>
+      <c r="Y40" s="22">
         <v>16</v>
       </c>
-      <c r="Z40" s="65"/>
-      <c r="AA40" s="20">
+      <c r="Z40" s="67"/>
+      <c r="AA40" s="23">
         <f>SUM(G40:Z40)</f>
         <v>200</v>
       </c>
-      <c r="AB40" s="20"/>
-      <c r="AC40" s="63"/>
-      <c r="AD40" s="63"/>
+      <c r="AB40" s="23"/>
+      <c r="AC40" s="65"/>
+      <c r="AD40" s="65"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
@@ -2832,78 +2836,78 @@
       <c r="AN40" s="3"/>
     </row>
     <row r="41" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="51" t="s">
+      <c r="A41" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="B41" s="51"/>
-      <c r="C41" s="51"/>
-      <c r="D41" s="51"/>
-      <c r="E41" s="51"/>
-      <c r="F41" s="51"/>
-      <c r="G41" s="19"/>
-      <c r="H41" s="19"/>
-      <c r="I41" s="19"/>
-      <c r="J41" s="19"/>
-      <c r="K41" s="53"/>
-      <c r="L41" s="53"/>
-      <c r="M41" s="19"/>
-      <c r="N41" s="19"/>
-      <c r="O41" s="19"/>
-      <c r="P41" s="19"/>
-      <c r="Q41" s="73"/>
-      <c r="R41" s="73"/>
-      <c r="S41" s="19"/>
-      <c r="T41" s="19"/>
-      <c r="U41" s="19"/>
-      <c r="V41" s="19"/>
-      <c r="W41" s="19"/>
-      <c r="X41" s="19"/>
-      <c r="Y41" s="19"/>
-      <c r="Z41" s="65"/>
-      <c r="AA41" s="20">
-        <f t="shared" ref="AA41:AA42" si="7">SUM(G41:Z41)</f>
+      <c r="B41" s="53"/>
+      <c r="C41" s="53"/>
+      <c r="D41" s="53"/>
+      <c r="E41" s="53"/>
+      <c r="F41" s="53"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="22"/>
+      <c r="I41" s="22"/>
+      <c r="J41" s="22"/>
+      <c r="K41" s="55"/>
+      <c r="L41" s="55"/>
+      <c r="M41" s="22"/>
+      <c r="N41" s="22"/>
+      <c r="O41" s="22"/>
+      <c r="P41" s="22"/>
+      <c r="Q41" s="75"/>
+      <c r="R41" s="75"/>
+      <c r="S41" s="22"/>
+      <c r="T41" s="22"/>
+      <c r="U41" s="22"/>
+      <c r="V41" s="22"/>
+      <c r="W41" s="22"/>
+      <c r="X41" s="22"/>
+      <c r="Y41" s="22"/>
+      <c r="Z41" s="67"/>
+      <c r="AA41" s="23">
+        <f t="shared" ref="AA41:AA42" si="6">SUM(G41:Z41)</f>
         <v>0</v>
       </c>
-      <c r="AB41" s="20"/>
-      <c r="AC41" s="63"/>
-      <c r="AD41" s="63"/>
+      <c r="AB41" s="23"/>
+      <c r="AC41" s="65"/>
+      <c r="AD41" s="65"/>
     </row>
     <row r="42" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="51" t="s">
+      <c r="A42" s="53" t="s">
         <v>45</v>
       </c>
-      <c r="B42" s="51"/>
-      <c r="C42" s="51"/>
-      <c r="D42" s="51"/>
-      <c r="E42" s="51"/>
-      <c r="F42" s="51"/>
-      <c r="G42" s="19"/>
-      <c r="H42" s="19"/>
-      <c r="I42" s="19"/>
-      <c r="J42" s="19"/>
-      <c r="K42" s="19"/>
-      <c r="L42" s="19"/>
-      <c r="M42" s="19"/>
-      <c r="N42" s="19"/>
-      <c r="O42" s="19"/>
-      <c r="P42" s="19"/>
-      <c r="Q42" s="19"/>
-      <c r="R42" s="19"/>
-      <c r="S42" s="19"/>
-      <c r="T42" s="19"/>
-      <c r="U42" s="19"/>
-      <c r="V42" s="19"/>
-      <c r="W42" s="19"/>
-      <c r="X42" s="19"/>
-      <c r="Y42" s="19"/>
-      <c r="Z42" s="65"/>
-      <c r="AA42" s="20">
-        <f t="shared" si="7"/>
+      <c r="B42" s="53"/>
+      <c r="C42" s="53"/>
+      <c r="D42" s="53"/>
+      <c r="E42" s="53"/>
+      <c r="F42" s="53"/>
+      <c r="G42" s="22"/>
+      <c r="H42" s="22"/>
+      <c r="I42" s="22"/>
+      <c r="J42" s="22"/>
+      <c r="K42" s="22"/>
+      <c r="L42" s="22"/>
+      <c r="M42" s="22"/>
+      <c r="N42" s="22"/>
+      <c r="O42" s="22"/>
+      <c r="P42" s="22"/>
+      <c r="Q42" s="22"/>
+      <c r="R42" s="22"/>
+      <c r="S42" s="22"/>
+      <c r="T42" s="22"/>
+      <c r="U42" s="22"/>
+      <c r="V42" s="22"/>
+      <c r="W42" s="22"/>
+      <c r="X42" s="22"/>
+      <c r="Y42" s="22"/>
+      <c r="Z42" s="67"/>
+      <c r="AA42" s="23">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AB42" s="20"/>
-      <c r="AC42" s="63"/>
-      <c r="AD42" s="63"/>
+      <c r="AB42" s="23"/>
+      <c r="AC42" s="65"/>
+      <c r="AD42" s="65"/>
     </row>
     <row r="43" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E43" s="2"/>
@@ -3194,6 +3198,16 @@
     <mergeCell ref="T29:U29"/>
     <mergeCell ref="T30:U30"/>
   </mergeCells>
+  <conditionalFormatting sqref="AD7:AI20">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
+      <formula>75</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ7:AN20">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"Failed"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.9" bottom="0.25" header="0" footer="0"/>
   <pageSetup paperSize="10000" scale="97" orientation="portrait" r:id="rId1"/>
